--- a/AAII_Financials/Yearly/ELUXY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ELUXY_YR_FIN.xlsx
@@ -789,7 +789,7 @@
         <v>10467800</v>
       </c>
       <c r="F9" s="3">
-        <v>11665500</v>
+        <v>11609700</v>
       </c>
       <c r="G9" s="3">
         <v>11241000</v>
@@ -840,7 +840,7 @@
         <v>1834100</v>
       </c>
       <c r="F10" s="3">
-        <v>1703800</v>
+        <v>1759600</v>
       </c>
       <c r="G10" s="3">
         <v>1698300</v>
@@ -1014,7 +1014,7 @@
         <v>10800</v>
       </c>
       <c r="F14" s="3">
-        <v>-10500</v>
+        <v>44800</v>
       </c>
       <c r="G14" s="3">
         <v>-81000</v>
@@ -1134,7 +1134,7 @@
         <v>12213400</v>
       </c>
       <c r="F17" s="3">
-        <v>13680600</v>
+        <v>13625100</v>
       </c>
       <c r="G17" s="3">
         <v>13034600</v>
@@ -1185,7 +1185,7 @@
         <v>88500</v>
       </c>
       <c r="F18" s="3">
-        <v>-311200</v>
+        <v>-255800</v>
       </c>
       <c r="G18" s="3">
         <v>-95300</v>
@@ -1257,7 +1257,7 @@
         <v>13400</v>
       </c>
       <c r="F20" s="3">
-        <v>45600</v>
+        <v>45700</v>
       </c>
       <c r="G20" s="3">
         <v>84600</v>
@@ -1308,7 +1308,7 @@
         <v>484000</v>
       </c>
       <c r="F21" s="3">
-        <v>89300</v>
+        <v>144700</v>
       </c>
       <c r="G21" s="3">
         <v>196900</v>
@@ -1869,7 +1869,7 @@
         <v>-13400</v>
       </c>
       <c r="F32" s="3">
-        <v>-45600</v>
+        <v>-45700</v>
       </c>
       <c r="G32" s="3">
         <v>-84600</v>
